--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Morango</t>
+          <t>Morango Médio</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,18 +473,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Morango Grande</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fruta</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Tomate</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Legume</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Verdura</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>KG</t>
         </is>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Morango Médio</t>
+          <t>Morango Grande</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -462,18 +462,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>CX</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Morango Grande</t>
+          <t>Morango Médio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -482,31 +482,51 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>CX</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Morango Pequeno</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fruta</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Tomate</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Verdura</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>KG</t>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CX</t>
         </is>
       </c>
     </row>
